--- a/pre-week-3/homework1_exercise1A.xlsx
+++ b/pre-week-3/homework1_exercise1A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan's River\Documents\DataAnalytics\pre-week-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF9A5EE-03AA-4C4D-B405-9FAC6D99B014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB53E6C1-231C-44B7-9289-BC1EE480825C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FAD7190E-3379-4975-8C7D-BF7D07E561BB}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{FAD7190E-3379-4975-8C7D-BF7D07E561BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1043,16 +1043,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
